--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_967_Aruba_Netherlands.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_967_Aruba_Netherlands.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rde47d599633548b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R90623d5297fc4e67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R62f45498d6e24045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3f908ec3052240a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1c1b656fcc2c4f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3b0e42533dc84761"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc9909c476d3d4de2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9b22e762820b4e8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R713b30b0e1dd41d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf67f87ca936c4a31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R104bdd5ec0034d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5c6819560c494b79"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ967CommercialTable" displayName="EEZ967CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ967CommercialTable" displayName="EEZ967CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ967FunctionalTable" displayName="EEZ967FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ967FunctionalTable" displayName="EEZ967FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ967ValidationTable" displayName="EEZ967ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ967ValidationTable" displayName="EEZ967ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4915,7 +4869,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45860fdb11a14c82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re185cac6ef124868"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4925,20 +4879,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4946,552 +4890,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1.2148812619999998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1.2148812619999998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$64,A2,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>192.5457041792367</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>192.5457041792367</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.612524955</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.2549999999102077</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>179.88709147568633</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.612524955</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>181.33155681924023</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$64,A3,'Species'!$U$2:$U$64))</x:f>
-        <x:v>111.07010368078508</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.2549999999102077</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>179.88709147568633</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>110.18533261122566</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0.8847710695594202</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.008029844341272</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.00802984434127197</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>26.0450976058</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.3123897416161014</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>205.300374511209</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>26.0450976058</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>213.35613834596896</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$64,A4,'Species'!$U$2:$U$64))</x:f>
-        <x:v>5556.88144801733</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.3123897416161014</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>205.300374511209</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>5347.068292651732</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>209.8131553655976</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.039238914463452</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.03923891446345199</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1.2148812619999998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.16</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>144.5439770745928</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1.2148812619999998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$64,A5,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>175.60376928288034</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.16</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>144.5439770745928</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>175.60376928288034</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.30626247700000003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.19</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>15.488166189124811</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.30626247700000003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>15.48816618912481</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$64,A6,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>4.743444141269015</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.19</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>15.488166189124811</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>4.743444141269015</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>413.1522516202</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.2857334652847308</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>193.07829953840317</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>413.1522516202</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>196.39108115172166</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$64,A7,'Species'!$U$2:$U$64))</x:f>
-        <x:v>81139.41737595922</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.2857334652847308</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>193.07829953840317</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>79770.73419329069</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1368.6831826685375</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0171577107382779</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.017157710738277925</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1406.1886521259999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.131852595326679</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1354.7295231189369</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1406.1886521259999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1669.5360259677198</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$64,A8,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2347682.614031346</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.131852595326679</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1354.7295231189369</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1905005.2821099164</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>442677.3319214296</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2323759078668464</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.23237590786684637</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>230.1380590455</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.293484757911755</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1965.5529959185908</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>230.1380590455</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2101.121304746914</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$64,A9,'Species'!$U$2:$U$64))</x:f>
-        <x:v>483547.9788936033</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.293484757911755</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1965.5529959185908</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>452348.55143177207</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>31199.42746183125</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.068972095440737</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.06897209544073686</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>369.07973908440005</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.482284264513924</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>3035.87764717823</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>369.07973908440005</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>3044.8842317339463</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$64,A10,'Species'!$U$2:$U$64))</x:f>
-        <x:v>1123805.0777905688</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.482284264513924</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>3035.87764717823</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1120480.9299127033</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3324.147877865471</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0029667152640647</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0029667152640647397</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d02e8d5a53b4000"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57ca398930854dc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5501,20 +5086,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5522,984 +5097,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.5990900901</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.5990900901</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$64,A2,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1310.6663084092595</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1310.6663084092595</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.1744970489</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.18</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1513.5612484362073</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.1744970489</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$64,A3,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>264.1119711815179</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.18</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>264.1119711815179</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1048.3360142922</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.359116449191662</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2286.211732689928</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1048.3360142922</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2325.161634130126</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$64,A4,'Species'!$U$2:$U$64))</x:f>
-        <x:v>2437550.680109115</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.359116449191662</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2286.211732689928</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2396718.0956762233</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>40832.58443289157</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.017036874093184</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.017036874093184013</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>15.8553556429</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.575647856983776</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>376.3984765548265</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>15.8553556429</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>382.2987341585605</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$64,A5,'Species'!$U$2:$U$64))</x:f>
-        <x:v>6061.482391914458</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.575647856983776</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>376.3984765548265</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>5967.931709222532</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>93.55068269192634</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0156755618612991</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.015675561861299113</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1.2170974828000003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.070798298645532</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1177.0591796263864</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1.2170974828000003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1178.6417432996545</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$64,A6,'Species'!$U$2:$U$64))</x:f>
-        <x:v>1434.5218988930137</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.070798298645532</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1177.0591796263864</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1432.5957646299082</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1.9261342631054958</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0013445064620885</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.001344506462088478</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>214.28270340259996</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.346599447884779</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2221.2602654256093</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>214.28270340259996</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2228.301626401337</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$64,A7,'Species'!$U$2:$U$64))</x:f>
-        <x:v>477486.49650168885</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.346599447884779</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2221.2602654256093</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>475977.6546361763</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1508.8418655125424</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0031699846638091</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0031699846638091824</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>0.306262478</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>0.306262478</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$64,A8,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>48.539331648847174</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>48.539331648847174</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1.214881262</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1.214881262</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$64,A9,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>248.04691708934044</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>248.04691708934044</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>665.6317271273</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.4219364196750965</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>264.20219393516237</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>665.6317271273</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>280.397114050219</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$64,A10,'Species'!$U$2:$U$64))</x:f>
-        <x:v>186641.21530675777</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.4219364196750965</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>264.20219393516237</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>175861.362659884</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>10779.85264687377</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0612974475110943</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.06129744751109436</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>364.1585398579</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.226095965451326</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1683.0459203148223</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>364.1585398579</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2245.8691726806446</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$64,A11,'Species'!$U$2:$U$64))</x:f>
-        <x:v>817852.4386352535</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.226095965451326</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1683.0459203148223</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>612895.5448556412</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>204956.89377961226</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.334407543830143</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.3344075438301431</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>103.4441518814</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.975991450983528</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>946.2185350239964</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>103.4441518814</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1030.5918011918786</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$64,A12,'Species'!$U$2:$U$64))</x:f>
-        <x:v>106608.6948102183</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.975991450983528</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>946.2185350239964</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>97880.7738500181</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>8727.920960200194</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0891689002538325</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.08916890025383244</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>0.30626247700000003</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.19</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>15.488166189124811</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>0.30626247700000003</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>15.48816618912481</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$64,A13,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>4.743444141269015</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.19</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>15.488166189124811</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>4.743444141269015</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>0.30626247700000003</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>0.30626247700000003</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$64,A14,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>62.530772031937914</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>62.530772031937914</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>1.214881262</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.03</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>107.1519305237606</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>1.214881262</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$64,A15,'Species'!$U$2:$U$64))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>130.1768725804426</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.03</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>130.1768725804426</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2.4297625239999996</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.18</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>151.35612484362088</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2.4297625239999996</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>151.5166481603521</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$64,A16,'Species'!$U$2:$U$64))</x:f>
-        <x:v>368.14947346211704</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.18</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>151.35612484362088</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>367.7594399228953</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0.3900335392217471</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0010605670361679</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.001060567036167778</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>2.429762526</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.3649999999999998</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>231.73946499684774</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>2.429762526</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>241.40481306314842</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$64,A17,'Species'!$U$2:$U$64))</x:f>
-        <x:v>586.5563683768734</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.3649999999999998</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>231.73946499684774</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>563.0718678446294</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>23.484500532243942</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.041707820747891</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.04170782074789094</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>26.0450976058</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.3123897416161014</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>205.300374511209</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>26.0450976058</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>213.35613834596896</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$64,A18,'Species'!$U$2:$U$64))</x:f>
-        <x:v>5556.88144801733</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.3123897416161014</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>205.300374511209</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>5347.068292651732</x:v>
       </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>209.8131553655976</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.039238914463452</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.03923891446345199</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bb296c2902048ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra521393e4356468a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6674,7 +5610,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6773,7 +5709,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>4042215.93256078</x:v>
+        <x:v>3563435.644190549</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6787,7 +5723,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>4042215.932560779</x:v>
+        <x:v>3775080.6743692975</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6801,7 +5737,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>9.313225746154785e-10</x:v>
+        <x:v>-478780.28837023024</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6815,7 +5751,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-267135.2581914817</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6826,9 +5762,9 @@
         <x:v>EEZ_967</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6840,47 +5776,19 @@
         <x:v>EEZ_967</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_967</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_967</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re256befd34c64013"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9826e55cd824b2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6927,7 +5835,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
